--- a/rules-template.xlsx
+++ b/rules-template.xlsx
@@ -583,7 +583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" style="21" min="1" max="1"/>
@@ -766,6 +766,20 @@
       <c r="A31" t="inlineStr">
         <is>
           <t>Дашборд → кнопка «Загрузить таблицу правил» → выберите этот файл. Чтобы правила сохранились для всех, войдите по паролю (дашборд сам предложит).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дополнительные стрелки</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Столбец «Доп. стрелки от блоков»: коды блоков через «;», от которых на схеме нужно нарисовать ещё стрелки в этот блок (кроме родителя). Только для наглядности: на подсчёт не влияет, блок по-прежнему считается от родителя или от «Брать из блока». Пустая ячейка убирает доп. стрелки, а если столбца в таблице нет, стрелки остаются прежними. То же можно сделать в панели блока в режиме правки.</t>
         </is>
       </c>
     </row>
@@ -780,7 +794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="21" min="1" max="1"/>
@@ -794,6 +808,7 @@
     <col width="26" customWidth="1" style="21" min="10" max="10"/>
     <col width="22" customWidth="1" style="21" min="11" max="11"/>
     <col width="22" customWidth="1" style="21" min="12" max="12"/>
+    <col width="30" customWidth="1" style="21" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" s="21">
@@ -855,6 +870,11 @@
       <c r="L1" s="22" t="inlineStr">
         <is>
           <t>Тип блока</t>
+        </is>
+      </c>
+      <c r="M1" s="22" t="inlineStr">
+        <is>
+          <t>Доп. стрелки от блоков (коды через ;)</t>
         </is>
       </c>
     </row>

--- a/rules-template.xlsx
+++ b/rules-template.xlsx
@@ -583,7 +583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" style="21" min="1" max="1"/>
@@ -737,7 +737,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Код блока (столбец A) у существующих блоков и родителя встроенных блоков — он останется прежним, а в сообщении о загрузке появится предупреждение. Название блока (столбец B) переименовать можно, оно сменится на схеме.</t>
+          <t>Код блока (столбец A) у существующих блоков менять нельзя: строка с другим кодом создаст новый блок. Название блока (столбец B) переименовать можно, оно сменится на схеме.</t>
         </is>
       </c>
     </row>
@@ -780,6 +780,20 @@
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Столбец «Доп. стрелки от блоков»: коды блоков через «;», от которых на схеме нужно нарисовать ещё стрелки в этот блок (кроме родителя). Только для наглядности: на подсчёт не влияет, блок по-прежнему считается от родителя или от «Брать из блока». Пустая ячейка убирает доп. стрелки, а если столбца в таблице нет, стрелки остаются прежними. То же можно сделать в панели блока в режиме правки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Столбец «Пунктир (возврат) от блоков»: коды блоков через «;», из которых в этот блок идёт пунктирная стрелка «возврат в ветку». Тоже только рисунок. Пустая ячейка убирает пунктир; если столбца нет, пунктир остаётся прежним.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">«Родитель (код)» теперь можно менять у любого блока, кроме «Все должники»: от родителя идёт сплошная стрелка, и блок отбирает должников из него (если не задано «Брать из блока»). Родителем нельзя сделать блок, который находится ниже, — получится круг.</t>
         </is>
       </c>
     </row>
@@ -794,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="21" min="1" max="1"/>
@@ -809,6 +823,7 @@
     <col width="22" customWidth="1" style="21" min="11" max="11"/>
     <col width="22" customWidth="1" style="21" min="12" max="12"/>
     <col width="30" customWidth="1" style="21" min="13" max="13"/>
+    <col width="30" customWidth="1" style="21" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" s="21">
@@ -875,6 +890,11 @@
       <c r="M1" s="22" t="inlineStr">
         <is>
           <t>Доп. стрелки от блоков (коды через ;)</t>
+        </is>
+      </c>
+      <c r="N1" s="22" t="inlineStr">
+        <is>
+          <t>Пунктир (возврат) от блоков (коды через ;)</t>
         </is>
       </c>
     </row>

--- a/rules-template.xlsx
+++ b/rules-template.xlsx
@@ -583,7 +583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A36"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" style="21" min="1" max="1"/>
@@ -794,6 +794,13 @@
       <c r="A36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">«Родитель (код)» теперь можно менять у любого блока, кроме «Все должники»: от родителя идёт сплошная стрелка, и блок отбирает должников из него (если не задано «Брать из блока»). Родителем нельзя сделать блок, который находится ниже, — получится круг.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Столбец «Цвет заливки»: цвет блока на схеме — Жёлтый, Оранжевый, Красный, Розовый, Фиолетовый, Синий, Голубой, Зелёный, Серый. Пустая ячейка — цвет по типу блока; если столбца нет, цвет не меняется. Цвет можно выбрать и в панели блока в режиме правки.</t>
         </is>
       </c>
     </row>
@@ -808,7 +815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="21" min="1" max="1"/>
@@ -824,6 +831,7 @@
     <col width="22" customWidth="1" style="21" min="12" max="12"/>
     <col width="30" customWidth="1" style="21" min="13" max="13"/>
     <col width="30" customWidth="1" style="21" min="14" max="14"/>
+    <col width="16" customWidth="1" style="21" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" s="21">
@@ -895,6 +903,11 @@
       <c r="N1" s="22" t="inlineStr">
         <is>
           <t>Пунктир (возврат) от блоков (коды через ;)</t>
+        </is>
+      </c>
+      <c r="O1" s="22" t="inlineStr">
+        <is>
+          <t>Цвет заливки</t>
         </is>
       </c>
     </row>
@@ -927,7 +940,7 @@
     <row r="40" ht="30" customHeight="1" s="21"/>
     <row r="42" ht="30" customHeight="1" s="21"/>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation sqref="D2:D500 G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Недопустимое значение" error="Выберите значение из списка." type="list">
       <formula1>=СписокКолонок</formula1>
     </dataValidation>
@@ -942,6 +955,9 @@
     </dataValidation>
     <dataValidation sqref="A2:A500 I2:I500 K2:K500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=СписокБлоков</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O2:O500">
+      <formula1>"Жёлтый,Оранжевый,Красный,Розовый,Фиолетовый,Синий,Голубой,Зелёный,Серый"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
